--- a/data/reports/now-2026-09-05-1019.xlsx
+++ b/data/reports/now-2026-09-05-1019.xlsx
@@ -10,6 +10,7 @@
     <sheet name="同時刻カット10時" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="日次ファネル" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="今日の時間別" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="カゴ落ち" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1400,4 +1401,173 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日付(JST)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>カゴ落ち件数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8/25-31 平均</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>先週基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>週内最多</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>セール開始日だが平均どおり</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-05 (〜10時)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>直近2日半(41件)の放置カート総額</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>218,831円</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>平均5,337円/件・最頻値3,980円</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Shopify abandonedCheckout=連絡先入力まで進んで離脱した人(メールアドレスが残っている)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>読み</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>件数は先週比フラット=チェックアウト自体の故障シグナルなし。完了率低下は「入力前に離脱・購入延期」側</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>